--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0101.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0101.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Vực Sâu III - Đợt Tiêu Diệt Quái Vật II</t>
+          <t>Đợt II - Sát Quái Vực Sâu III</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Vực Sâu III - Đợt Tiêu Diệt Quái Vật III</t>
+          <t>Đợt III - Sát Quái Vực Sâu III</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Vực Sâu IV - Đợt Tiêu Diệt Quái Vật I</t>
+          <t>Đợt I - Sát Quái Vực Sâu IV</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Vực Sâu IV - Đợt Tiêu Diệt Quái Vật II</t>
+          <t>Đợt II - Sát Quái Vực Sâu IV</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Vực Sâu IV - Đợt Tiêu Diệt Quái Vật III</t>
+          <t>Đợt III - Sát Quái Vực Sâu IV</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Vực Sâu V - Đợt Tiêu Diệt Quái Vật I</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng V - Lần 1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vực Sâu V - Đợt Tiêu Diệt Quái Vật II</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng V - Lần 2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực V - Làn 3</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng V - Lần 3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VI - Làn 1</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VI - Lần 1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VI - Làn 2</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VI - Lần 2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VI - Làn 3</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VI - Lần 3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VII - Làn 1</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VII - Lần 1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VII - Làn 2</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VII - Lần 2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VII - Làn 3</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VII - Lần 3</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VIII - Làn 1</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VIII - Lần 1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VIII - Làn 2</t>
+          <t>Sóng Tiêu Diệt Quái Vực Tầng VIII - Lần 2</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực VIII - Làn 3</t>
+          <t>Đợt III - Sát Quái Vực VIII</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực IX - Làn 1</t>
+          <t>Đợt I - Sát Quái Vực Sâu IX</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực IX - Làn 2</t>
+          <t>Đợt II - Sát Quái Vực Sâu IX</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực IX - Làn 3</t>
+          <t>Đợt III - Sát Quái Vực Sâu IX</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực X - Làn 1</t>
+          <t>Đợt I - Sát Quái Vực X</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực X - Làn 2</t>
+          <t>Đợt II - Sát Quái Vực X</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực X - Làn 3</t>
+          <t>Đợt III - Sát Quái Vực X</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XI - Làn 1</t>
+          <t>Đợt I - Sát Quái Vực XI</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XI - Làn 2</t>
+          <t>Đợt II - Sát Quái Vực XI</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XI - Làn 3</t>
+          <t>Đợt III - Sát Quái Vực XI</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XII - Làn 1</t>
+          <t>Đợt I - Sát Quái Vực XII</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XII - Làn 2</t>
+          <t>Đợt II - Sát Quái Vực XII</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XII - Làn 3</t>
+          <t>Đợt III - Sát Quái Vực XII</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XIII - Làn 1</t>
+          <t>Đợt I - Sát Quái Vực XIII</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XIII - Làn 2</t>
+          <t>Đợt II - Sát Quái Vực XIII</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Trừ Quái Vực Vực XIII - Làn 3</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIII - Làn Sóng 3</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIV I</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIV - Làn Sóng 1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIV II</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIV - Làn Sóng 2</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIV III</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIV - Làn Sóng 3</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XV I</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XV - Làn Sóng 1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XV II</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XV - Làn Sóng 2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XV III</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XV - Làn Sóng 3</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVI I</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XVI - Làn Sóng 1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVI II</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XVI - Làn Sóng 2</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVI III</t>
+          <t>Hố Sâu XVI - Làn Sóng Quét Quái Vật III</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVII I</t>
+          <t>Hố Sâu XVII - Làn Sóng Quét Quái Vật I</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVII II</t>
+          <t>Hố Sâu XVII - Làn Sóng Quét Quái Vật II</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVII III</t>
+          <t>Hố Sâu XVII - Làn Sóng Quét Quái Vật III</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVIII I</t>
+          <t>Hố Sâu XVIII - Làn Sóng Quét Quái Vật I</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVIII II</t>
+          <t>Hố Sâu XVIII - Làn Sóng Quét Quái Vật II</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XVIII III</t>
+          <t>Hố Sâu XVIII - Làn Sóng Quét Quái Vật III</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIX I</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIX - Làn Sóng 1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIX II</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIX - Làn Sóng 2</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XIX III</t>
+          <t>Đợt Tàn Sát Quái Vật Vực XIX - Làn Sóng 3</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XX I</t>
+          <t>Hố Sâu XX - Làn Sóng Quét Quái Vật I</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XX II</t>
+          <t>Hố Sâu XX - Làn Sóng Quét Quái Vật II</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đợt Tiễu Quái Vực XX III</t>
+          <t>Hố Sâu XX - Làn Sóng Quét Quái Vật III</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Phó bản Scar II đã mở khóa, nhiệm vụ Scar I đã hoàn thành</t>
+          <t>Vết Sẹo II đã mở khóa, nhiệm vụ Vết Sẹo I hoàn thành</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Phó bản Scar II đã mở khóa, nhiệm vụ Scar I đã hoàn thành, phán xét phía máy khách</t>
+          <t>Vết Sẹo II đã mở khóa, nhiệm vụ Vết Sẹo I hoàn thành, phán quyết phía máy khách</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Tương tác với công tắc phó bản 4600</t>
+          <t>Tương tác với công tắc Dungeon 4600</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Đã tiêu diệt đợt quái vật đầu tiên trong phó bản 4600</t>
+          <t>Đợt quái đầu tiên trong dungeon 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Đã tiêu diệt đợt quái vật thứ hai trong phó bản 4600</t>
+          <t>Đợt quái thứ hai trong hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Đã tiêu diệt đợt quái vật thứ ba trong phó bản 4600</t>
+          <t>Đợt quái thứ ba ở hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Đã tiêu diệt đợt quái vật thứ tư trong phó bản 4600</t>
+          <t>Đợt quái thứ tư trong hầm 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Đã tiêu diệt đợt quái vật thứ năm trong phó bản 4600</t>
+          <t>Đợt quái vật thứ năm ở hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Đã hoàn thành thu thập phần thưởng trong phó bản 4600</t>
+          <t>Hoàn tất thu thập phần thưởng trong hầm 4600.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tương tác với lối ra dungeon 4600</t>
+          <t>Tương tác với lối ra Dungeon 4600</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 80</t>
+          <t>Cấp Liên Minh đạt 80</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Tương tác với công tắc dungeon 180012300</t>
+          <t>Tương tác với công tắc Dungeon 180012300</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên trong dungeon 180012300</t>
+          <t>Đợt quái đầu tiên trong dungeon 180012300 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai trong dungeon 180012300</t>
+          <t>Đợt quái thứ hai trong hầm ngục 180012300 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ năm trong dungeon 180012300</t>
+          <t>Đợt quái vật thứ năm ở hầm ngục 180012300 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hoàn thành thu thập phần thưởng trong dungeon 180012300</t>
+          <t>Hoàn tất thu thập phần thưởng trong hầm 180012300.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tương tác với lối ra dungeon 180012300</t>
+          <t>Tương tác với lối ra Dungeon 180012300</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ ba trong dungeon 180012300</t>
+          <t>Làn quái thứ ba trong hầm ngục 180012300 đã bị tiêu diệt.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ tư trong dungeon 180012300</t>
+          <t>Đợt quái thứ tư trong hầm 180012300 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Tương tác với công tắc dungeon 4600</t>
+          <t>Tương tác với công tắc Dungeon 4600</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật đầu tiên trong dungeon 4600</t>
+          <t>Đợt quái đầu tiên trong dungeon 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ hai trong dungeon 4600</t>
+          <t>Đợt quái thứ hai trong hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ năm trong dungeon 4600</t>
+          <t>Đợt quái vật thứ năm ở hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Hoàn thành thu thập phần thưởng trong dungeon 4600</t>
+          <t>Hoàn tất thu thập phần thưởng trong hầm 4600.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Tương tác với lối ra dungeon 4600</t>
+          <t>Tương tác với lối ra Dungeon 4600</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ ba trong dungeon 4600</t>
+          <t>Đợt quái thứ ba ở hầm ngục 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật thứ tư trong dungeon 4600</t>
+          <t>Đợt quái thứ tư trong hầm 4600 đã bị tiêu diệt</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kiểm tra trạng thái bước dungeon</t>
+          <t>Đang kiểm tra trạng thái bước Tổ Tacet</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Tháp Nexus Jinzhou đã được mở khóa chưa</t>
+          <t>Kiểm tra xem Tháp Nexus Jinzhou đã mở khóa chưa</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Kiểm tra xem chức năng Tacet Field đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem chức năng Tổ Tacet đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Kiểm tra xem chức năng online đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem chức năng trực tuyến đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Đã kích hoạt phiên bản Tháp Nghịch Cảnh một lần</t>
+          <t>Phiên bản Tháp Nghịch Cảnh Một Lần đã kích hoạt</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Kiểm tra xem nhiệm vụ Hiệp Hội Tiên Phong đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem nhiệm vụ Hiệp Hội Tiên Phong đã kích hoạt chưa</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Bãi Than Vãn Aix - Aix Tang Thương</t>
+          <t>Hoàn thành Nhiệm Vụ Whining Aix's Mire - Mourning Aix</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhận được một ít bột mì</t>
+          <t>Nhận một bịch bột mì</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Nhận được một ít dầu ăn</t>
+          <t>Nhận một chai dầu ăn</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Lời Mở Đầu trong Nhiệm Vụ Chính để mở khóa</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 để mở khóa</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20</t>
+          <t>Đạt Cấp Độ Liên Minh 20</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Đến Tháp Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim"</t>
+          <t>Đến Tháp Chuông trong nhiệm vụ chính "Lửa Trong Tim"</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 35</t>
+          <t>Đạt Cấp Độ Liên Minh 35</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker</t>
+          <t>Cetus Kẻ Phá Thủy Triều</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Chi Suspended Monster (originally Whiff Whaff)</t>
+          <t>Quái Vật Chi Treo Lơ Lửng (tên gốc: Whiff Whaff)</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Furnace Pincer Beast (originally Snip Snap)</t>
+          <t>Quái Thú Kẹp Lò (tên gốc: Snip Snap)</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Heartless Puppet (originally A Zizi)</t>
+          <t>Con Rối Vô Tâm (trước đây là A Zizi)</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Lãnh Đạo Lưu Đày</t>
+          <t>Thủ Lĩnh Lưu Đày</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Little Fire Wolf</t>
+          <t>Sói Lửa Nhỏ</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Human Exiles - Male Barehand</t>
+          <t>Lưu dân - Nam tay không</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Human Exiles - Female Barehand</t>
+          <t>Lưu dân - Nữ tay không</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Human Exiles - Male Sniper</t>
+          <t>Những Kẻ Lưu Vong Loài Người - Xạ Thủ Nam</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Human Exiles - Female Crowbar</t>
+          <t>Lưu dân - Nữ xà beng</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Human Exiles - Female Flamethrower</t>
+          <t>Lưu dân - Nữ súng phun lửa</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Human Exiles - Female Chainsaw</t>
+          <t>Lưu dân - Nữ cưa máy</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Human Exiles - Female Electric Blade</t>
+          <t>Lưu dân - Nữ kiếm điện</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Little Thorny Mushroom</t>
+          <t>Nấm Gai Nhỏ</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Fractsidus Thruster</t>
+          <t>Động Cơ Phản Lực Fractsidus</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Khi nhân vật ở vị trí I</t>
+          <t>Khi ta đứng ở vị trí I</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Khi nhân vật ở vị trí II</t>
+          <t>Khi ta đứng ở vị trí II</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Khi nhân vật ở vị trí III</t>
+          <t>Khi ta đứng ở vị trí III</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nhận 3 Nhân vật</t>
+          <t>Nhận được 3 Nhân Vật.</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Khi nhân vật ở vị trí IV</t>
+          <t>Khi ta đứng ở vị trí IV</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Khi nhận được thẻ kinh nghiệm nhân vật cơ bản</t>
+          <t>Khi nhận được thẻ kinh nghiệm nhân vật Cơ Bản</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Khi nhận được thẻ kinh nghiệm nhân vật trung cấp</t>
+          <t>Khi nhận được thẻ kinh nghiệm nhân vật Medium</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Khi nhận được thẻ kinh nghiệm nhân vật Cao cấp</t>
+          <t>Khi nhận được thẻ kinh nghiệm nhân vật Cao Cấp</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Khi nhận được thẻ kinh nghiệm nhân vật Cao cấp Premium</t>
+          <t>Khi nhận được thẻ kinh nghiệm nhân vật cao cấp</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Teleport - Small Huabiao</t>
+          <t>Dịch chuyển - Bia Huabiao Nhỏ</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Teleport - Large Huabiao - Console</t>
+          <t>Dịch chuyển - Bia Huabiao Lớn - Bảng Điều Khiển</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Teleport - Medium Huabiao</t>
+          <t>Dịch chuyển - Bia Huabiao Trung</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Thu thập - Plant001 - Hoa Súng</t>
+          <t>Thu thập - Thực vật001 - Sen Nước</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Thu thập - Plant011 - Bittberry</t>
+          <t>Thu thập - Thực vật011 - Quả Bitterberry</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Thu thập - Plant101 - Thực vật Đầu mùa 1</t>
+          <t>Thu thập - Plant101 - Thực vật sơ khai 1</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Thu thập - Plant102 - Thực vật Đầu mùa 2</t>
+          <t>Thu thập - Plant102 - Thực vật sơ khai 2</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Thu thập - Plant103 - Thực vật Rộng lá 1</t>
+          <t>Thu thập - Plant103 - Thực vật lá rộng 1</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Thu thập - Plant104 - Thực vật Rộng lá 2</t>
+          <t>Thu thập - Plant104 - Thực vật lá rộng 2</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thu thập - Plant105 - Thực vật Rộng lá 3</t>
+          <t>Thu thập - Plant105 - Thực vật lá rộng 3</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Thu thập - Plant107 - Thực vật Rộng lá 5</t>
+          <t>Thu thập - Plant107 - Thực vật lá rộng 5</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Thu thập - Plant109 - Thực vật Nước 1</t>
+          <t>Thu thập - Plant109 - Thực vật thủy sinh 1</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Thu thập - Plant110 - Thực vật Nước 2</t>
+          <t>Thu thập - Plant110 - Thực vật thủy sinh 2</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Thu thập - Plant115 - Thực vật Núi 1</t>
+          <t>Thu thập - Plant115 - Thực vật vùng núi 1</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Thu thập - Plant116 - Thực vật Núi 2</t>
+          <t>Thu thập - Plant116 - Thực vật vùng núi 2</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Thu thập - Plant601 - Trứng Chim</t>
+          <t>Thu thập - Plant601 - Trứng chim</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Chương 2</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Hồi 2</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tháp Nghịch Cảnh được mở khóa sau khi hoàn thành Nhiệm Vụ Hướng Dẫn "Cô Đơn Trong Vực Sâu"</t>
+          <t>Tháp Nghịch Cảnh sẽ mở khóa sau khi hoàn thành Nhiệm Vụ Hướng Dẫn "Cô Đơn Trong Vực Sâu"</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 10 để mở khóa "Chúng Ta Hứa, Chúng Ta Sẽ Giao Hàng"</t>
+          <t>Đạt Cấp Độ Liên Minh 10 để mở khóa "Lời Hứa, Lời Giữ"</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 10 hoặc hoàn thành Chương II để mở khóa Cột Mốc</t>
+          <t>Đạt Cấp Độ Liên Minh 10 hoặc hoàn thành Chương II để mở khóa Cột Mốc</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 8</t>
+          <t>Đạt Cấp Độ Liên Minh 8</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mở khóa Baiting</t>
+          <t>Mở khóa Kỹ Năng Dụ Dỗ</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "Thước Đo Quá Khứ" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Cán Cân Quá Khứ" để mở khóa</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Đến Bờ Biển Cuối Cùng" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Tận Cùng Bờ Vực" để mở khóa</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Chương III Nhiệm Vụ Chính "Điều Hôm Qua Khóc, Hôm Nay Hát Ca" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hoàn thành “Chống Lại Mọi Tỷ Lệ” trong "Khi Đêm Gõ Cửa" để mở khóa</t>
+          <t>Hoàn thành "Chống Lại Mọi Tỷ Lệ" trong "Khi Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hoàn thành Câu Chuyện Nhân Vật thứ hai để mở khóa</t>
+          <t>Hoàn thành Câu Chuyện Nhân Vật thứ hai để mở khóa.</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Dưới Ánh Trăng Định Mệnh" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Dưới Ánh Trăng Định Mệnh" để mở khóa</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời"</t>
+          <t>Hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "By Sun's Burning Hand"</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 5</t>
+          <t>Đạt Cấp Độ Liên Minh 5</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Dưới Bàn Tay Cháy Bỏng Của Mặt Trời"</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Chương V Nhiệm Vụ Chính "Bóng Tối Của Vinh Quang" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi V "Bóng Tối Của Vinh Quang" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Chương VII Nhiệm Vụ Chính "Những Kẻ Bắt Giấc Mơ Trong Khu Vườn Bí Mật" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VII "Những Giấc Mộng Trong Vườn Bí Mật" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Chương VIII Nhiệm Vụ Chính "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" để mở khóa</t>
+          <t>Hoàn thành Chương II Hồi VIII "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương III Chương I Nhiệm Vụ Chính "Điều Cháy Bên Dưới Vùng Đất Băng Giá" để mở khóa</t>
+          <t>Hoàn thành Chương III Hồi I "Điều Gì Cháy Bên Dưới Băng Giá" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Xác định tiêu diệt Crownless</t>
+          <t>Xác định kẻ giết Crownless</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Lớn - Xác định phần thưởng Crownless</t>
+          <t>Tổ Tacet cỡ lớn - Xác định phần thưởng Crownless</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Xác định tiêu diệt rùa</t>
+          <t>Xác định kẻ giết rùa</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Làm mới xác định Lĩnh vực Tacet Vừa</t>
+          <t>Xác định làm mới Tổ Tacet Cỡ Trung</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Determine Mephis kill</t>
+          <t>Xác định kẻ giết Mephis</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Vừa - Xác định kích hoạt tương tác</t>
+          <t>Xác định kích hoạt tương tác Tổ Tacet Cỡ Trung</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Vừa - Xác định phần thưởng</t>
+          <t>Xác định phần thưởng Tổ Tacet Cỡ Trung</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Vừa - Xác định tiêu diệt quái vật</t>
+          <t>Xác định tiêu diệt quái vật trong Tổ Tacet Cỡ Trung</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Lớn - Xác định phần thưởng rùa</t>
+          <t>Tổ Tacet cỡ lớn - Xác định phần thưởng Turtle</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Lớn - Xác định phần thưởng Mephis</t>
+          <t>Tổ Tacet cỡ lớn - Xác định phần thưởng Mephis</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Lĩnh vực Tacet Lớn - Trước khi bắt đầu Crownless</t>
+          <t>Tổ Tacet cỡ lớn - Crownless trước khi bắt đầu</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Xác định tiêu diệt Hiệp sĩ</t>
+          <t>Quyết Tâm Sát Phạt Của Hiệp Sĩ</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Kết thúc nhiệm vụ cửa hàng vũ khí</t>
+          <t>Nhiệm vụ cửa hàng vũ khí đã kết thúc</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Nhiệm vụ quán trà chưa kết thúc</t>
+          <t>Nhiệm vụ quán trà chưa hoàn thành</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Nhiệm vụ nói chuyện với Mortefi chưa kết thúc</t>
+          <t>Nói chuyện với Mortefi xong nhưng chưa kết thúc nhiệm vụ</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Kết thúc nhiệm vụ vào Hoa Biểu</t>
+          <t>Kết thúc nhiệm vụ Hoa Biểu</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Xác định xem có phải là NPC</t>
+          <t>Xác định có phải NPC không</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Kết thúc nhiệm vụ trước khi kích hoạt Hoa Biểu nhỏ</t>
+          <t>Hoàn thành nhiệm vụ trước khi kích hoạt tiểu Hoa Biểu</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Phát hiện Crownless sắp chết</t>
+          <t>Phát hiện Crownless đang hấp hối</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Phát hiện hoàn thành cốt truyện đầu tiên</t>
+          <t>Kiểm tra xem cốt truyện đầu tiên đã hoàn thành chưa</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Phát hiện hoàn thành cốt truyện thứ hai</t>
+          <t>Kiểm tra xem cốt truyện thứ hai đã hoàn thành chưa</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Xác định xem có phải là người chơi</t>
+          <t>Xác định có phải người chơi không</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Kiểm tra cấp độ tài khoản người chơi</t>
+          <t>Đang kiểm tra cấp độ tài khoản</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hoàn thành phó bản đột phá</t>
+          <t>Hoàn thành hầm đột phá</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ Tacet Field nhỏ nào</t>
+          <t>Hoàn thành một Tổ Tacet nhỏ.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Jinzhou Commission Unlocked</t>
+          <t>Ủy ban Jinzhou Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Đánh bại Thundering Mephis</t>
+          <t>Hạ gục Thundering Mephis</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Mở khóa ở Ascension 1</t>
+          <t>Mở khóa khi đạt Thăng Tinh 1</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Mở khóa ở Ascension 2</t>
+          <t>Mở khóa khi đạt Thăng Tinh 2</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Mở khóa ở Ascension 3</t>
+          <t>Mở khóa khi đạt Thăng Tinh 3</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Mở khóa ở Ascension 4</t>
+          <t>Mở khóa khi Tiến Hóa 4</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Mở khóa ở Ascension 5</t>
+          <t>Mở khóa khi Tiến Hóa 5</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Bình Minh Ló Rạng Trên Sóng Bóng Tối"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Dawn Breaks on Dark Tides"</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tiêu diệt 3 quái vật trong Jinzhou Mainline - Ancient Collector</t>
+          <t>Tiêu diệt 3 quái vật ở Jinzhou Mainline - Ancient Collector</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Tiêu diệt 3 quái vật trong Jinzhou Mainline - Ancient Collector</t>
+          <t>Tiêu diệt 3 quái vật ở Jinzhou Mainline - Ancient Collector</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi hoàn thành nhiệm vụ ở Jinzhou</t>
+          <t>Mở khóa sau khi hoàn thành các nhiệm vụ ở Jinzhou</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Hoàn thành thu thập Tacetite trong tháp</t>
+          <t>Thu thập Tacetite trong tháp</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Hoàn thành thu thập Tacetite trong tàn tích</t>
+          <t>Thu thập Tacetite trong đống đổ nát</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tiêu diệt quái vật nhỏ trong trạm giám sát</t>
+          <t>Tiêu diệt lũ quái nhỏ tại trạm giám sát</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tiêu diệt Mephis</t>
+          <t>Tiêu Diệt Mephis</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ ở Jinzhou</t>
+          <t>Hoàn thành các nhiệm vụ ở Jinzhou đi nào.</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ tiêu diệt Mephis ở Dragon's Tear</t>
+          <t>Hoàn thành nhiệm vụ tiêu diệt Mephis tại Dragon's Tear</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tiêu diệt quái vật nhỏ trong trại wanderer</t>
+          <t>Tiêu diệt lũ quái nhỏ trong trại của kẻ lang thang</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Đến bên ngoài trạm giám sát</t>
+          <t>Đến gần trạm giám sát đi</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mở Rương Cung Ứng trong tàn tích</t>
+          <t>Mở Rương Vật Tư trong đống đổ nát</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Mở Rương Cung Cấp trong phế tích</t>
+          <t>Mở Rương Vật Tư trong đống đổ nát</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Mở Rương Cung Cấp trong phế tích</t>
+          <t>Mở Rương Vật Tư trong đống đổ nát</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Vào Tacet Field</t>
+          <t>Bước vào Tổ Tacet</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Tiêu diệt bức tường Rương Cung Cấp trong phế tích</t>
+          <t>Phá hủy bức tường bảo vệ Rương Cung Ứng trong đống đổ nát</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tiêu diệt quái vật Rương Cung Cấp</t>
+          <t>Giết quái vật bảo vệ Rương Cung Ứng</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Lấy kho báu Baizhi</t>
+          <t>Tìm được kho báu Baizhi</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ chính cấp 5</t>
+          <t>Hoàn thành Nhiệm vụ chính Cấp 5</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Sau cuộc trò chuyện với Bác Ji</t>
+          <t>Sau cuộc trò chuyện với Bác Kỷ</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Để lấy Rương Cung Cấp</t>
+          <t>Cho Rương Vật Tư</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Để lấy Rương Cung Cấp</t>
+          <t>Cho Rương Vật Tư</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Dọn sạch Tacet Field</t>
+          <t>Dọn sạch Tổ Tacet</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 5</t>
+          <t>Đạt Cấp Độ Liên Minh 5</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tiêu diệt quái vật nhỏ trong Tacet Field</t>
+          <t>Giết quái vật nhỏ trong Tổ Tacet</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Dọn sạch Tacet Field giả</t>
+          <t>Dọn sạch Tổ Tacet giả</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Tiêu diệt đợt quái vật nhỏ thứ ba tại trạm giám sát</t>
+          <t>Tiêu diệt đợt quái nhỏ thứ ba tại trạm giám sát</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Mid-Tune Wall Destruction 1</t>
+          <t>Phá Hủy Tường Giữa Nhịp 1</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Mid-Tune Wall Destruction 1</t>
+          <t>Phá Hủy Tường Giữa Nhịp 1</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Mid-Tune Wall Destruction 1</t>
+          <t>Phá Hủy Tường Giữa Nhịp 1</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Small Tacet Field</t>
+          <t>Tổ Tacet Nhỏ</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Nhiệm vụ phụ 3001: Bia mộ Levitator</t>
+          <t>Nhiệm Vụ Phụ Bia Mộ Levitator 3001</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Nhiệm vụ phụ 3001: Kiểm tra Levitator</t>
+          <t>Nhiệm Vụ Phụ Kiểm Tra Levitator 3001</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 14</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nhiệm vụ phụ 2004: Rương Cung Cấp Levitator</t>
+          <t>Nhiệm Vụ Phụ Rương Cung Cấp Levitator 2004</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành Nửa đầu Chương I</t>
+          <t>Nửa đầu Chương I hoàn thành</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hoàn thành Nửa sau Chương I</t>
+          <t>Nửa sau Chương I hoàn thành</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Hoàn thành Nửa sau Chương I</t>
+          <t>Nửa sau Chương I hoàn thành</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Hoàn thành Nửa sau Chương I</t>
+          <t>Nửa sau Chương I hoàn thành</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mặt hàng 1 đã bán hết</t>
+          <t>Vật phẩm 1 đã bán hết</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Mặt hàng 2 đã bán hết</t>
+          <t>Vật phẩm 2 đã bán hết</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Mặt hàng 1 đã bán hết</t>
+          <t>Vật phẩm 1 đã bán hết</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Mặt hàng 2 đã bán hết</t>
+          <t>Vật phẩm 2 đã bán hết</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Đã hoàn thành thử nghiệm gameplay Lampy Cat</t>
+          <t>Thử nghiệm lối chơi Mèo Đèn hoàn tất</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Internet Disconnecting</t>
+          <t>Mất kết nối mạng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tên có thể dài tối đa 6 ký tự Trung Quốc hoặc 12 chữ cái</t>
+          <t>Tên có thể dài tối đa 6 ký tự Trung Quốc hoặc 12 chữ cái.</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Echo hạng trên Elite</t>
+          <t>Chất lượng Echo trên cấp Tinh Anh</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Echo hạng trên Overlord</t>
+          <t>Chất lượng Echo trên cấp Chúa Tể</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Echo hạng trên Calamity</t>
+          <t>Chất lượng Echo trên cấp Thảm Họa</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Không thể gỡ Echo chính</t>
+          <t>Không thể gỡ bỏ Echo chính.</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Quay lại trò chơi đơn</t>
+          <t>Quay lại chế độ chơi đơn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>COST Limit Reached</t>
+          <t>ĐÃ ĐẠT GIỚI HẠN CHI PHÍ</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Bạn đã hết lượt Triệu Tập trong Banner này</t>
+          <t>Ngươi đã hết lượt triệu hồi trong Banner này.</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Xác nhận thay thế</t>
+          <t>Xác nhận đổi mới</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Số lượt Triệu Tập trong toàn bộ Banner đã đạt giới hạn hôm nay</t>
+          <t>Số lần Triệu Hoán trong toàn bộ Banner hôm nay đã đạt giới hạn</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Dữ liệu Cửa hàng đã được làm mới, vui lòng kiểm tra dữ liệu mới nhất</t>
+          <t>Dữ liệu Cửa Hàng đã được làm mới, hãy kiểm tra dữ liệu mới nhất</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Xác nhận thoát</t>
+          <t>Xác nhận thoát?</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Xin lỗi, chức năng nạp tiền hiện chưa mở cho thiết bị iOS trong đợt thử nghiệm này</t>
+          <t>Xin lỗi, chức năng nạp năng lượng chưa mở cho thiết bị iOS trong đợt thử nghiệm này.</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Kết thúc và hoàn tất</t>
+          <t>Kết thúc và Xác nhận</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Xác nhận thoát</t>
+          <t>Xác nhận thoát?</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Exit Game</t>
+          <t>Thoát Game</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Dữ liệu Cửa Hàng đã được làm mới, vui lòng kiểm tra dữ liệu mới nhất</t>
+          <t>Dữ liệu Cửa Hàng đã được làm mới, hãy kiểm tra dữ liệu mới nhất</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Kích hoạt Casket Sonar</t>
+          <t>Kích hoạt Cảm Biến Quan Tài</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Kích hoạt Lootmapper</t>
+          <t>Kích hoạt Bản Đồ Chiến Lợi Phẩm</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kích hoạt Điểm dịch chuyển</t>
+          <t>Kích hoạt Điểm Dịch Chuyển</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Kích hoạt Điểm dịch chuyển</t>
+          <t>Kích hoạt Điểm Dịch Chuyển</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Gadgetpod</t>
+          <t>Hộp Công Cụ</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Exchange Tips</t>
+          <t>Mẹo Đổi</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>COST khả dụng không đủ</t>
+          <t>Không đủ COST khả dụng</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>COST khả dụng không đủ</t>
+          <t>Không đủ COST khả dụng</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Enhance Tips</t>
+          <t>Mẹo Nâng cấp</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Data Bank Experience</t>
+          <t>Điểm Kinh Nghiệm Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Exit Game</t>
+          <t>Thoát Game</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Ban</t>
+          <t>Cấm</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Sonata Effect</t>
+          <t>Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Chức năng thanh toán chưa mở trong đợt thử nghiệm này</t>
+          <t>Chức năng thanh toán chưa được mở trong đợt thử nghiệm này</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Clear Patch</t>
+          <t>Mảnh Thanh Tẩy</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
